--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.74.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.74.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.74.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.74.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -597,24 +597,28 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L24: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L24: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -645,7 +649,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -657,7 +661,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ should</t>
+          <t>L17: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • should</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -669,7 +673,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L3: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -677,7 +681,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L105: line starts with punctuation glued to text :: .Collyer, 507).</t>
+          <t>L17: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • should</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -710,11 +714,7 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: question under the following Order :â€”</t>
-        </is>
-      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr"/>
@@ -726,7 +726,11 @@
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L105: line starts with punctuation glued to text :: .Collyer, 507).</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -747,7 +751,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -950,7 +954,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -989,7 +993,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1106,7 +1110,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
